--- a/data/processed/positivacao/2023-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2023-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25439,7 +25439,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B966" t="inlineStr"/>
@@ -36713,7 +36713,7 @@
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr"/>
@@ -65657,7 +65657,7 @@
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2514" t="inlineStr"/>
@@ -67328,12 +67328,12 @@
       <c r="A2579" t="inlineStr"/>
       <c r="B2579" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 9 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 8.626,35
+          <t>Vendedor 1 - VENDEDOR 01: positivou 9 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 8.626,35
 Vendedor 18 - LOJA: positivou 134 cliente(s), não positivou 727 cliente(s) - Total vendido: R$ 73.070,08
-Vendedor 3 - FERNANDA: positivou 105 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 172.001,19
-Vendedor 4 - DANIELA: positivou 90 cliente(s), não positivou 575 cliente(s) - Total vendido: R$ 55.882,51
+Vendedor 3 - VENDEDOR 03: positivou 105 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 172.001,19
+Vendedor 4 - VENDEDOR 04: positivou 90 cliente(s), não positivou 575 cliente(s) - Total vendido: R$ 55.882,51
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 513,40
-Vendedor 8 - RAFAEL: positivou 1 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 120,26</t>
+Vendedor 8 - VENDEDOR 08: positivou 1 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 120,26</t>
         </is>
       </c>
       <c r="C2579" t="inlineStr"/>
